--- a/data/trans_orig/IQ23_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>38623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57394</t>
+          <t>57607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58111</t>
+          <t>58377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>49401</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62533</t>
+          <t>62720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112231</t>
+          <t>111929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132457</t>
+          <t>131314</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86461</t>
+          <t>87780</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114398</t>
+          <t>114716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93480</t>
+          <t>94958</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>123082</t>
+          <t>123225</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187807</t>
+          <t>189755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>228054</t>
+          <t>228901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286694</t>
+          <t>285001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>314408</t>
+          <t>313706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>345514</t>
+          <t>345117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>375499</t>
+          <t>374526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>642759</t>
+          <t>642665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>683501</t>
+          <t>682975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>50306</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29945</t>
+          <t>30245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46754</t>
+          <t>47723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65711</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91058</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121189</t>
+          <t>120866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139651</t>
+          <t>139157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105411</t>
+          <t>105173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122647</t>
+          <t>122785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233428</t>
+          <t>231403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258776</t>
+          <t>256873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37109</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>146346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182586</t>
+          <t>182479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156193</t>
+          <t>155392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190164</t>
+          <t>191441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310947</t>
+          <t>310905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363284</t>
+          <t>361365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>513045</t>
+          <t>512705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>549094</t>
+          <t>550480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1000496</t>
+          <t>1004034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1054812</t>
+          <t>1054463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33191</t>
+          <t>33121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64445</t>
+          <t>62787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>56387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71088</t>
+          <t>71000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>51395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65656</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111409</t>
+          <t>112576</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132409</t>
+          <t>132923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>38359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>102991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>133639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102992</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136458</t>
+          <t>132313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>216664</t>
+          <t>215643</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>257699</t>
+          <t>259416</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>306248</t>
+          <t>309275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>339943</t>
+          <t>340757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>339554</t>
+          <t>341092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>372594</t>
+          <t>373359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>659497</t>
+          <t>658789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>702580</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29282</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47439</t>
+          <t>46720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>37753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56968</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70868</t>
+          <t>71503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97609</t>
+          <t>97497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111792</t>
+          <t>112586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131047</t>
+          <t>132310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111781</t>
+          <t>111540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131159</t>
+          <t>130618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231018</t>
+          <t>229808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>257533</t>
+          <t>256882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30267</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162579</t>
+          <t>161945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200260</t>
+          <t>200562</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173091</t>
+          <t>172870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213812</t>
+          <t>211396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347625</t>
+          <t>346331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402828</t>
+          <t>401493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>515624</t>
+          <t>517416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>558156</t>
+          <t>557587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1018699</t>
+          <t>1017388</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1075360</t>
+          <t>1076158</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30887</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36237</t>
+          <t>36423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49100</t>
+          <t>49808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76207</t>
+          <t>76457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94006</t>
+          <t>94548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111687</t>
+          <t>113625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143384</t>
+          <t>144781</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133798</t>
+          <t>132701</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167392</t>
+          <t>167462</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>256084</t>
+          <t>254275</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>299555</t>
+          <t>298236</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>316306</t>
+          <t>316268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>349905</t>
+          <t>346305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>309484</t>
+          <t>307511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341481</t>
+          <t>342376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>637530</t>
+          <t>636104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>681878</t>
+          <t>682300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>50729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72961</t>
+          <t>71489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68741</t>
+          <t>69763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105184</t>
+          <t>105400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135264</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94068</t>
+          <t>95286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115755</t>
+          <t>116252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114552</t>
+          <t>113822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134880</t>
+          <t>135137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215628</t>
+          <t>216512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245217</t>
+          <t>246111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31855</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186700</t>
+          <t>188877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225389</t>
+          <t>226691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212308</t>
+          <t>212559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414722</t>
+          <t>412495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>472665</t>
+          <t>468156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>30102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52334</t>
+          <t>51448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>31586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84014</t>
+          <t>84820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96783</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141722</t>
+          <t>141059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136249</t>
+          <t>136466</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178522</t>
+          <t>176929</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>249619</t>
+          <t>248026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>307562</t>
+          <t>310209</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>308261</t>
+          <t>308559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>356542</t>
+          <t>355661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>330276</t>
+          <t>330843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>373329</t>
+          <t>372823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649775</t>
+          <t>648742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>708687</t>
+          <t>713674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30124</t>
+          <t>30838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47510</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69280</t>
+          <t>69917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96139</t>
+          <t>95697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99060</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116267</t>
+          <t>115745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127587</t>
+          <t>127288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147843</t>
+          <t>147970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231334</t>
+          <t>232299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258359</t>
+          <t>258396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,82 +8281,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3613</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18565</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>16845</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>26606</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8017</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3610</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17103</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>16845</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>10666</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>26946</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153329</t>
+          <t>153609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201879</t>
+          <t>201161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199124</t>
+          <t>198071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247200</t>
+          <t>247350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366547</t>
+          <t>369063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437859</t>
+          <t>435049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>446675</t>
+          <t>447342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>496221</t>
+          <t>496429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>962550</t>
+          <t>965413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1035668</t>
+          <t>1033705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7425</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1830</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5425</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6870</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26087</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20527</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33741</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22416</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15969</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16280</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29691</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26087</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19748</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32962</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>39282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57607</t>
+          <t>58619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48134</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>61808</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>65,5%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>65400</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>58377</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>72132</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>58168</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>71469</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>72,95%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>65,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>80,46%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49401</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62720</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>65,5%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111929</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>131314</t>
+          <t>131592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85487</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85487</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85487</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89646</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>89646</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>89646</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85487</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85487</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>85487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6677</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3215</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11456</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11306</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6844</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17182</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6694</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17855</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6677</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3474</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12202</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107850</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>93584</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122296</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>22,64%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>100777</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>87780</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>114716</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>87604</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>115780</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>24,39%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>21,25%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>107850</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>94958</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123225</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189755</t>
+          <t>187840</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>228901</t>
+          <t>227816</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>361778</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>347730</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>375904</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>75,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>301024</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>285001</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>313706</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>283963</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>314547</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>72,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>68,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>361778</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>345117</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>374526</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>75,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>642665</t>
+          <t>642103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682975</t>
+          <t>682612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>476305</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>476305</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>476305</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>624</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>413107</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>413107</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>413107</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>476305</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>476305</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>476305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8269</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1087</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3527</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8184</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1753,67 +1753,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>38494</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30323</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47694</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>40552</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32559</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50306</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32683</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51222</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38494</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>47723</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67402</t>
+          <t>66802</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>92841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>114594</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>105205</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>123238</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>130748</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>120866</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>139157</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>138733</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>114594</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>105173</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>122785</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231403</t>
+          <t>229909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256873</t>
+          <t>257592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,21%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156960</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156960</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156960</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172388</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172388</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172388</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156960</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156960</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13953</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8682</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20590</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>14223</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8796</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20996</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20426</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13953</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>8597</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21323</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>172431</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>154836</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>191198</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>163746</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>146346</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>182479</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>146150</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>181168</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>172431</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>155392</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>191441</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310905</t>
+          <t>310177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361365</t>
+          <t>361539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -2317,74 +2317,74 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>532367</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>512900</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>550520</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>74,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>71,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>478826</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>515681</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>480522</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>515664</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>76,38%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>532367</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>512705</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>550480</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>74,07%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>71,33%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1535</t>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1004034</t>
+          <t>1004191</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1054463</t>
+          <t>1058095</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>718752</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>718752</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>718752</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>675141</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>675141</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>718752</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>718752</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>718752</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2699</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6857</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19805</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34016</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25844</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19137</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33121</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19473</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33426</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27182</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>42373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62787</t>
+          <t>63474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>59010</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>52176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66387</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>60,53%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>63826</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56387</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71000</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>56414</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>70459</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>69,1%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>61,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>59010</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51395</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>66081</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112576</t>
+          <t>111705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132923</t>
+          <t>133133</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19009</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13088</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27910</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>8721</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4834</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14794</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15395</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19009</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12848</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>27304</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38359</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3347,107 +3347,107 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>118139</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>103728</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>134486</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>118490</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>102991</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>133639</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>104627</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>133655</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>26,24%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>236629</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>215812</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>258101</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>22,81%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>118139</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>102503</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>132313</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>26,76%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>236629</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>215643</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>259416</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>357298</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>341005</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>373386</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>75,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>466</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>324323</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>309275</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>340757</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>309324</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>338190</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>71,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>68,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>357298</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>341092</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>373359</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>658789</t>
+          <t>659322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>702276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>451535</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>451535</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>451535</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6548</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6036</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2653</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11368</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11787</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2651</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47235</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37894</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>57426</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37188</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28342</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46720</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28596</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>45723</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47235</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37753</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56659</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71503</t>
+          <t>72057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97497</t>
+          <t>97342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>121006</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>110580</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>122802</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>112586</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>132310</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>113749</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>132042</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>121006</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>111540</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130618</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>70,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229808</t>
+          <t>231315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256882</t>
+          <t>256956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170892</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170892</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170892</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166026</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166026</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170892</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170892</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21660</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15029</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30722</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17456</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11417</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24964</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25465</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21660</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15510</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30817</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50686</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>192556</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>173554</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>211516</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>181522</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>161945</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>200562</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>163119</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>200197</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>25,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,81%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>192556</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>172870</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>211396</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346331</t>
+          <t>347688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401493</t>
+          <t>401842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>537314</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>517554</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>556219</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>74,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>491483</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>531483</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>490900</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>528676</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>537314</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>517416</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>557587</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1017388</t>
+          <t>1016741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1076158</t>
+          <t>1075236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>751530</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>751530</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>751530</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>709929</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>709929</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>751530</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>751530</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>751530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,107 +4833,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3411</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3461</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24157</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18133</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30963</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16748</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11854</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11974</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24157</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17601</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31047</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>49505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43023</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36184</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49250</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>72,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>42630</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36693</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47524</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36805</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47404</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>71,79%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>43023</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>36423</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49808</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>63,41%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>76827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94548</t>
+          <t>94232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67850</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67850</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67850</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67850</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67850</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4071</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12858</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9149</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16075</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5089</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14708</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7535</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4038</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12486</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>150127</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>133617</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>166107</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>31,01%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>27,6%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128326</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113625</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>144781</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>112759</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>143887</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>27,31%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>24,18%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>30,81%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>150127</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>132701</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>167462</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254275</t>
+          <t>255258</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>298236</t>
+          <t>300900</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>326411</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>310964</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>343219</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>497</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>332469</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>316268</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>346305</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>315482</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>348110</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>326411</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>307511</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>342376</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>636104</t>
+          <t>634904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682300</t>
+          <t>681137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>484073</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>484073</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>484073</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>469944</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>469944</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>469944</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>484073</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>484073</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>484073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5750,67 +5750,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7617</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>2997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7133</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6998</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3168</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7072</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58309</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48511</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68552</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61440</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>50729</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>71489</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50833</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>72028</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>36,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>58309</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>48650</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>69763</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105400</t>
+          <t>106101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134018</t>
+          <t>135210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>124842</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114435</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>135124</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>105495</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95286</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116252</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95457</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>116060</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>62,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>124842</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>113822</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>135137</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>67,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216512</t>
+          <t>214891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246111</t>
+          <t>244183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186319</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186319</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186319</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169931</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169931</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169931</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186319</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186319</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11373</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6534</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17383</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>12145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7578</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19089</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7840</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11373</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6835</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17898</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>232593</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>211213</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>253967</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>206513</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>188877</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>226691</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>185452</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>225030</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>29,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>232593</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>212559</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>254974</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412495</t>
+          <t>413010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>468156</t>
+          <t>468639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>473777</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>515717</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>64,18%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>716</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>458336</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>497620</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>461458</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>500683</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>472693</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>515355</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>945678</t>
+          <t>945109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1002204</t>
+          <t>1001563</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>738242</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>699253</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>699253</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>738242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,107 +6888,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2448</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19991</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26573</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18466</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10967</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26616</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22284</t>
+          <t>16134</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>27939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51448</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36317</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>74,42%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34836</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26686</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>42335</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>65,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31586</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>34636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>74072</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>57663</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84820</t>
+          <t>74079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53302</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>53302</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53302</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>102378</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>102378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115306</t>
+          <t>102378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1649</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13010</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7547</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3663</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14008</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>137570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>117606</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155095</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>123148</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>95990</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>141059</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>26,94%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>155947</t>
+          <t>117565</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>136466</t>
+          <t>104569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176929</t>
+          <t>132086</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>279095</t>
+          <t>255136</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>248026</t>
+          <t>231917</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>310209</t>
+          <t>279466</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>330978</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>312822</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>350235</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>426</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>326499</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>308559</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>355661</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>352960</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>330843</t>
+          <t>288142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>372823</t>
+          <t>317224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>679459</t>
+          <t>634725</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648742</t>
+          <t>609311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>713674</t>
+          <t>658677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>473774</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>473774</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>473774</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>457194</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>457194</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>457194</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514622</t>
+          <t>429227</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514622</t>
+          <t>429227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514622</t>
+          <t>429227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>971817</t>
+          <t>903002</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>971817</t>
+          <t>903002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>971817</t>
+          <t>903002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37840</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29204</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46884</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>38314</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30838</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>47910</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>37299</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>75139</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>62875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>87303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>128737</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>119510</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>137462</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>108151</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99006</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115745</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138177</t>
+          <t>109476</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127288</t>
+          <t>101033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147970</t>
+          <t>118239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>246327</t>
+          <t>238212</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232299</t>
+          <t>225601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258396</t>
+          <t>250661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>147745</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>147745</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>147745</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>148023</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331094</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331094</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331094</t>
+          <t>316441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7492</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16163</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8828</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4497</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15313</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>195402</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>173560</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>217575</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>179928</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>153609</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>201161</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>221586</t>
+          <t>170999</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198071</t>
+          <t>153821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247350</t>
+          <t>189776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>401513</t>
+          <t>366401</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369063</t>
+          <t>339697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>435049</t>
+          <t>395115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>473783</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>74,24%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>630</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>447342</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>496429</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>71,32%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>67,96%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442734</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>504217</t>
+          <t>423999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>554632</t>
+          <t>460413</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>965413</t>
+          <t>909859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1033705</t>
+          <t>966511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>698925</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>658242</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>658242</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>658242</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>622896</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>622896</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>759975</t>
+          <t>622896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1418217</t>
+          <t>1321821</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1418217</t>
+          <t>1321821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1418217</t>
+          <t>1321821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">

--- a/data/trans_orig/IQ23_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R2-Estudios-trans_orig.xlsx
@@ -726,213 +726,213 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3404</v>
+        <v>26087</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1329</v>
+        <v>20527</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7425</v>
+        <v>33741</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.03982406118557792</v>
+        <v>0.305158063850095</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.01554166313087989</v>
+        <v>0.2401213870647613</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.08685794166330757</v>
+        <v>0.3946908021968908</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1830</v>
+        <v>22416</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>573</v>
+        <v>16280</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>4880</v>
+        <v>29691</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.02041277141215769</v>
+        <v>0.2500541868231511</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.006393096162142672</v>
+        <v>0.1815994961195858</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.05443980103211118</v>
+        <v>0.3312079730217882</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>5234</v>
+        <v>48503</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>2411</v>
+        <v>39282</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>9855</v>
+        <v>58619</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.02988798106462882</v>
+        <v>0.2769519763873056</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.01376437094693476</v>
+        <v>0.2242969272730001</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.05626907998970519</v>
+        <v>0.3347114616562868</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>26087</v>
+        <v>55996</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>20527</v>
+        <v>48134</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>33741</v>
+        <v>61808</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.305158063850095</v>
+        <v>0.6550178749643271</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2401213870647613</v>
+        <v>0.5630603632534009</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3946908021968908</v>
+        <v>0.7230161655486158</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>22416</v>
+        <v>65400</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>16280</v>
+        <v>58168</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>29691</v>
+        <v>71469</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2500541868231511</v>
+        <v>0.7295330417646912</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.1815994961195858</v>
+        <v>0.6488668687348078</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3312079730217882</v>
+        <v>0.797234161174412</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>48503</v>
+        <v>121395</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>39282</v>
+        <v>111100</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>58619</v>
+        <v>131592</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2769519763873056</v>
+        <v>0.6931600425480656</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2242969272730001</v>
+        <v>0.6343753002220927</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3347114616562868</v>
+        <v>0.7513859896897934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>55996</v>
+        <v>3404</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48134</v>
+        <v>1329</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>61808</v>
+        <v>7425</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6550178749643271</v>
+        <v>0.03982406118557792</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5630603632534009</v>
+        <v>0.01554166313087989</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7230161655486158</v>
+        <v>0.08685794166330757</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>65400</v>
+        <v>1830</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>58168</v>
+        <v>573</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>71469</v>
+        <v>4880</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.7295330417646912</v>
+        <v>0.02041277141215769</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6488668687348078</v>
+        <v>0.006393096162142672</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.797234161174412</v>
+        <v>0.05443980103211118</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>121395</v>
+        <v>5234</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>111100</v>
+        <v>2411</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>131592</v>
+        <v>9855</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.6931600425480656</v>
+        <v>0.02988798106462882</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6343753002220927</v>
+        <v>0.01376437094693476</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7513859896897934</v>
+        <v>0.05626907998970519</v>
       </c>
     </row>
     <row r="7">
@@ -1014,213 +1014,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>6677</v>
+        <v>107850</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3215</v>
+        <v>93584</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>11456</v>
+        <v>122296</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01401849745975742</v>
+        <v>0.2264304114004351</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.006749677505307469</v>
+        <v>0.1964785746448447</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02405181710870084</v>
+        <v>0.2567604537836726</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>11306</v>
+        <v>100777</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>6694</v>
+        <v>87604</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>17855</v>
+        <v>115780</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02736722448602809</v>
+        <v>0.2439498488745831</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01620282475840243</v>
+        <v>0.2120610609742537</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.04322086381266996</v>
+        <v>0.2802674281266163</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>17983</v>
+        <v>208627</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>12020</v>
+        <v>187840</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>25920</v>
+        <v>227816</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.02021861264399515</v>
+        <v>0.2345677064465467</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01351501666383532</v>
+        <v>0.2111954743825135</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.02914324468735767</v>
+        <v>0.256142743537214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>163</v>
+        <v>545</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107850</v>
+        <v>361778</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>93584</v>
+        <v>347730</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>122296</v>
+        <v>375904</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2264304114004351</v>
+        <v>0.7595510911398075</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1964785746448447</v>
+        <v>0.7300579466177468</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.2567604537836726</v>
+        <v>0.7892089445365507</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>155</v>
+        <v>451</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>100777</v>
+        <v>301024</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>87604</v>
+        <v>283963</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>115780</v>
+        <v>314547</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2439498488745831</v>
+        <v>0.7286829266393888</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2120610609742537</v>
+        <v>0.6873832732021723</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2802674281266163</v>
+        <v>0.7614185377428021</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>318</v>
+        <v>996</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>208627</v>
+        <v>662802</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>187840</v>
+        <v>642103</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>227816</v>
+        <v>682612</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2345677064465467</v>
+        <v>0.7452136809094582</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2111954743825135</v>
+        <v>0.7219408747345434</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.256142743537214</v>
+        <v>0.7674864429799666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>545</v>
+        <v>10</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>361778</v>
+        <v>6677</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>347730</v>
+        <v>3215</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>375904</v>
+        <v>11456</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7595510911398075</v>
+        <v>0.01401849745975742</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.7300579466177468</v>
+        <v>0.006749677505307469</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7892089445365507</v>
+        <v>0.02405181710870084</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>451</v>
+        <v>18</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>301024</v>
+        <v>11306</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>283963</v>
+        <v>6694</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>314547</v>
+        <v>17855</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7286829266393888</v>
+        <v>0.02736722448602809</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6873832732021723</v>
+        <v>0.01620282475840243</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7614185377428021</v>
+        <v>0.04322086381266996</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>996</v>
+        <v>28</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>662802</v>
+        <v>17983</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>642103</v>
+        <v>12020</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>682612</v>
+        <v>25920</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7452136809094582</v>
+        <v>0.02021861264399515</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.7219408747345434</v>
+        <v>0.01351501666383532</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7674864429799666</v>
+        <v>0.02914324468735767</v>
       </c>
     </row>
     <row r="11">
@@ -1302,213 +1302,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3872</v>
+        <v>38494</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1327</v>
+        <v>30323</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>8269</v>
+        <v>47694</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02466728981369476</v>
+        <v>0.2452502076892985</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.008454022421622987</v>
+        <v>0.1931893617489044</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.05268308849782639</v>
+        <v>0.3038577683643202</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1087</v>
+        <v>40552</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>32683</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>3888</v>
+        <v>51222</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.006306843984095226</v>
+        <v>0.2352396466944187</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>0.1895877550539743</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.02255484936284561</v>
+        <v>0.2971302411478887</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>4959</v>
+        <v>79047</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>2169</v>
+        <v>66802</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>9304</v>
+        <v>92841</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01505703584635431</v>
+        <v>0.2400104638176517</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.006585377995666782</v>
+        <v>0.2028323777016734</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.0282507294433824</v>
+        <v>0.2818942923390684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>38494</v>
+        <v>114594</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>30323</v>
+        <v>105205</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>47694</v>
+        <v>123238</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2452502076892985</v>
+        <v>0.7300825024970067</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1931893617489044</v>
+        <v>0.670267205376616</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3038577683643202</v>
+        <v>0.7851531637644849</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>40552</v>
+        <v>130748</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>32683</v>
+        <v>120303</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>51222</v>
+        <v>138733</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2352396466944187</v>
+        <v>0.758453509321486</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1895877550539743</v>
+        <v>0.697864097584197</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2971302411478887</v>
+        <v>0.8047716590384588</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>118</v>
+        <v>359</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>79047</v>
+        <v>245342</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>66802</v>
+        <v>229909</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>92841</v>
+        <v>257592</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2400104638176517</v>
+        <v>0.744932500335994</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2028323777016734</v>
+        <v>0.6980723527080654</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2818942923390684</v>
+        <v>0.7821276792465217</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>114594</v>
+        <v>3872</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>105205</v>
+        <v>1327</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>123238</v>
+        <v>8269</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7300825024970067</v>
+        <v>0.02466728981369476</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.670267205376616</v>
+        <v>0.008454022421622987</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7851531637644849</v>
+        <v>0.05268308849782639</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>190</v>
+        <v>2</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>130748</v>
+        <v>1087</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>120303</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>138733</v>
+        <v>3888</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.758453509321486</v>
+        <v>0.006306843984095226</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.697864097584197</v>
+        <v>0</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8047716590384588</v>
+        <v>0.02255484936284561</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>359</v>
+        <v>8</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>245342</v>
+        <v>4959</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>229909</v>
+        <v>2169</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>257592</v>
+        <v>9304</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.744932500335994</v>
+        <v>0.01505703584635431</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6980723527080654</v>
+        <v>0.006585377995666782</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7821276792465217</v>
+        <v>0.0282507294433824</v>
       </c>
     </row>
     <row r="15">
@@ -1590,213 +1590,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>13953</v>
+        <v>172431</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8682</v>
+        <v>154836</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>20590</v>
+        <v>191198</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01941324674307896</v>
+        <v>0.2399040162411295</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.0120789446216887</v>
+        <v>0.2154236104859574</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02864647059571432</v>
+        <v>0.2660139011447235</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>23</v>
+        <v>249</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>14223</v>
+        <v>163746</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>8940</v>
+        <v>146150</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>20426</v>
+        <v>181168</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02106632777329644</v>
+        <v>0.2425363542128633</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.01324141891628579</v>
+        <v>0.2164728860574858</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03025468291728948</v>
+        <v>0.2683416773859439</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>44</v>
+        <v>510</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>28176</v>
+        <v>336178</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>20741</v>
+        <v>310177</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>37442</v>
+        <v>361539</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.02021392680079684</v>
+        <v>0.2411790054767531</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.01488023048456707</v>
+        <v>0.2225260289796842</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.02686179726386644</v>
+        <v>0.2593733399079382</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>261</v>
+        <v>798</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>172431</v>
+        <v>532367</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>154836</v>
+        <v>512900</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>191198</v>
+        <v>550520</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2399040162411295</v>
+        <v>0.7406827370157915</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2154236104859574</v>
+        <v>0.7135974101213347</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2660139011447235</v>
+        <v>0.7659389149678545</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>249</v>
+        <v>737</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>163746</v>
+        <v>497172</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>146150</v>
+        <v>480522</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>181168</v>
+        <v>515664</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2425363542128633</v>
+        <v>0.7363973180138402</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2164728860574858</v>
+        <v>0.7117351437053366</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2683416773859439</v>
+        <v>0.7637877192766752</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>510</v>
+        <v>1535</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>336178</v>
+        <v>1029539</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>310177</v>
+        <v>1004191</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>361539</v>
+        <v>1058095</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2411790054767531</v>
+        <v>0.7386070677224501</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2225260289796842</v>
+        <v>0.7204221284864539</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2593733399079382</v>
+        <v>0.7590931700408142</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>798</v>
+        <v>21</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>532367</v>
+        <v>13953</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>512900</v>
+        <v>8682</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>550520</v>
+        <v>20590</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7406827370157915</v>
+        <v>0.01941324674307896</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.7135974101213347</v>
+        <v>0.0120789446216887</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7659389149678545</v>
+        <v>0.02864647059571432</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>737</v>
+        <v>23</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>497172</v>
+        <v>14223</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>480522</v>
+        <v>8940</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>515664</v>
+        <v>20426</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7363973180138402</v>
+        <v>0.02106632777329644</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.7117351437053366</v>
+        <v>0.01324141891628579</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7637877192766752</v>
+        <v>0.03025468291728948</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1535</v>
+        <v>44</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1029539</v>
+        <v>28176</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1004191</v>
+        <v>20741</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1058095</v>
+        <v>37442</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.7386070677224501</v>
+        <v>0.02021392680079684</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.7204221284864539</v>
+        <v>0.01488023048456707</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7590931700408142</v>
+        <v>0.02686179726386644</v>
       </c>
     </row>
     <row r="19">
@@ -2109,205 +2109,205 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
+        <v>27182</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>19805</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>34016</v>
+      </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
+        <v>0.3153636273047435</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2297813610439769</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.3946551918520714</v>
+      </c>
       <c r="J4" s="5" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2699</v>
+        <v>25844</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>703</v>
+        <v>19473</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>6234</v>
+        <v>33426</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.02921643444735138</v>
+        <v>0.2797932417084174</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.007606769314647216</v>
+        <v>0.2108127079173605</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.06749315796300745</v>
+        <v>0.3618741400078571</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>2699</v>
+        <v>53026</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>708</v>
+        <v>42373</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>6662</v>
+        <v>63474</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.01511350446552301</v>
+        <v>0.2969632580701196</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.003962828483215959</v>
+        <v>0.2373039131096991</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.03731115402082697</v>
+        <v>0.3554774727971702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>27182</v>
+        <v>59010</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>19805</v>
+        <v>52176</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>34016</v>
+        <v>66387</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3153636273047435</v>
+        <v>0.6846363726952565</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2297813610439769</v>
+        <v>0.6053448081479287</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.3946551918520714</v>
+        <v>0.7702186389560233</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>25844</v>
+        <v>63826</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>19473</v>
+        <v>56414</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>33426</v>
+        <v>70459</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2797932417084174</v>
+        <v>0.6909903238442313</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2108127079173605</v>
+        <v>0.6107441206848402</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3618741400078571</v>
+        <v>0.7627985614690074</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>53026</v>
+        <v>122836</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>42373</v>
+        <v>111705</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>63474</v>
+        <v>133133</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.2969632580701196</v>
+        <v>0.6879232374643574</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2373039131096991</v>
+        <v>0.6255823631309513</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3554774727971702</v>
+        <v>0.7455855737268076</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>59010</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>52176</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>66387</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="6" t="n">
-        <v>0.6846363726952565</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.6053448081479287</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.7702186389560233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="5" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>63826</v>
+        <v>2699</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>56414</v>
+        <v>703</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>70459</v>
+        <v>6234</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.6909903238442313</v>
+        <v>0.02921643444735138</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.6107441206848402</v>
+        <v>0.007606769314647216</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.7627985614690074</v>
+        <v>0.06749315796300745</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>122836</v>
+        <v>2699</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>111705</v>
+        <v>708</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>133133</v>
+        <v>6662</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.6879232374643574</v>
+        <v>0.01511350446552301</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6255823631309513</v>
+        <v>0.003962828483215959</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7455855737268076</v>
+        <v>0.03731115402082697</v>
       </c>
     </row>
     <row r="7">
@@ -2389,213 +2389,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>19009</v>
+        <v>118139</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>13088</v>
+        <v>103728</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>27910</v>
+        <v>134486</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.03844582688593363</v>
+        <v>0.2389314468547726</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02647074801317247</v>
+        <v>0.209786092758608</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.05644779707907645</v>
+        <v>0.2719923238284297</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>13</v>
+        <v>175</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>8721</v>
+        <v>118490</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4951</v>
+        <v>104627</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>15395</v>
+        <v>133655</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01931512626067812</v>
+        <v>0.262416769859273</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01096562429353699</v>
+        <v>0.2317139060985518</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.0340958066254225</v>
+        <v>0.2960012783502984</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>27731</v>
+        <v>236629</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>19869</v>
+        <v>215812</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>37461</v>
+        <v>258101</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.02931437192949134</v>
+        <v>0.2501414476463787</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02100391814504817</v>
+        <v>0.2281361444806063</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.03960051063785366</v>
+        <v>0.2728402725442901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>171</v>
+        <v>510</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>118139</v>
+        <v>357298</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103728</v>
+        <v>341005</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>134486</v>
+        <v>373386</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2389314468547726</v>
+        <v>0.7226227262592938</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.209786092758608</v>
+        <v>0.6896714978527206</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.2719923238284297</v>
+        <v>0.7551600970340084</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>175</v>
+        <v>466</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>118490</v>
+        <v>324323</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>104627</v>
+        <v>309324</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>133655</v>
+        <v>338190</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.262416769859273</v>
+        <v>0.7182681038800489</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2317139060985518</v>
+        <v>0.6850502047276865</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.2960012783502984</v>
+        <v>0.7489790260889894</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>346</v>
+        <v>976</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>236629</v>
+        <v>681620</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>215812</v>
+        <v>659322</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>258101</v>
+        <v>702276</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2501414476463787</v>
+        <v>0.7205441804241299</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2281361444806063</v>
+        <v>0.6969729531859146</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.2728402725442901</v>
+        <v>0.7423792495700916</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>510</v>
+        <v>27</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>357298</v>
+        <v>19009</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>341005</v>
+        <v>13088</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>373386</v>
+        <v>27910</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.7226227262592938</v>
+        <v>0.03844582688593363</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6896714978527206</v>
+        <v>0.02647074801317247</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7551600970340084</v>
+        <v>0.05644779707907645</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>466</v>
+        <v>13</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>324323</v>
+        <v>8721</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>309324</v>
+        <v>4951</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>338190</v>
+        <v>15395</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7182681038800489</v>
+        <v>0.01931512626067812</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6850502047276865</v>
+        <v>0.01096562429353699</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7489790260889894</v>
+        <v>0.0340958066254225</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>976</v>
+        <v>40</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>681620</v>
+        <v>27731</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>659322</v>
+        <v>19869</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>702276</v>
+        <v>37461</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7205441804241299</v>
+        <v>0.02931437192949134</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6969729531859146</v>
+        <v>0.02100391814504817</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7423792495700916</v>
+        <v>0.03960051063785366</v>
       </c>
     </row>
     <row r="11">
@@ -2677,213 +2677,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2651</v>
+        <v>47235</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>650</v>
+        <v>37894</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>6548</v>
+        <v>57426</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01551097646056557</v>
+        <v>0.2764042773774642</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.003806449971348142</v>
+        <v>0.2217396028087287</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03831903278246462</v>
+        <v>0.3360370378836292</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>6036</v>
+        <v>37188</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>2742</v>
+        <v>28596</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>11787</v>
+        <v>45723</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.03635646285800553</v>
+        <v>0.2239867500505974</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.0165159286986955</v>
+        <v>0.1722400001017537</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.07099384740939005</v>
+        <v>0.2753987076052697</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>8687</v>
+        <v>84423</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>4672</v>
+        <v>72057</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>14393</v>
+        <v>97342</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.02578317985053565</v>
+        <v>0.2505740572696227</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.01386789483781396</v>
+        <v>0.2138708202713495</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.04272049986127065</v>
+        <v>0.2889196799277731</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>47235</v>
+        <v>121006</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>37894</v>
+        <v>110580</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>57426</v>
+        <v>130396</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2764042773774642</v>
+        <v>0.7080847461619703</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2217396028087287</v>
+        <v>0.6470743001888337</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3360370378836292</v>
+        <v>0.7630293835999067</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>37188</v>
+        <v>122802</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>28596</v>
+        <v>113749</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>45723</v>
+        <v>132042</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2239867500505974</v>
+        <v>0.7396567870913971</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1722400001017537</v>
+        <v>0.6851255138601962</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2753987076052697</v>
+        <v>0.795310569786399</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>120</v>
+        <v>345</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>84423</v>
+        <v>243808</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>72057</v>
+        <v>231315</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>97342</v>
+        <v>256956</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2505740572696227</v>
+        <v>0.7236427628798416</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2138708202713495</v>
+        <v>0.6865628897202636</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2889196799277731</v>
+        <v>0.7626651479673939</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>171</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>121006</v>
+        <v>2651</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>110580</v>
+        <v>650</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>130396</v>
+        <v>6548</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7080847461619703</v>
+        <v>0.01551097646056557</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6470743001888337</v>
+        <v>0.003806449971348142</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7630293835999067</v>
+        <v>0.03831903278246462</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>174</v>
+        <v>8</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>122802</v>
+        <v>6036</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>113749</v>
+        <v>2742</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>132042</v>
+        <v>11787</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7396567870913971</v>
+        <v>0.03635646285800553</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6851255138601962</v>
+        <v>0.0165159286986955</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.795310569786399</v>
+        <v>0.07099384740939005</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>345</v>
+        <v>12</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>243808</v>
+        <v>8687</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>231315</v>
+        <v>4672</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>256956</v>
+        <v>14393</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7236427628798416</v>
+        <v>0.02578317985053565</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6865628897202636</v>
+        <v>0.01386789483781396</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7626651479673939</v>
+        <v>0.04272049986127065</v>
       </c>
     </row>
     <row r="15">
@@ -2965,213 +2965,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>21660</v>
+        <v>192556</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>15029</v>
+        <v>173554</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>30722</v>
+        <v>211516</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02882130600209834</v>
+        <v>0.2562184092622987</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01999755982558853</v>
+        <v>0.2309344619126076</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0408788372306081</v>
+        <v>0.2814467573237918</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>25</v>
+        <v>267</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>17456</v>
+        <v>181522</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>11542</v>
+        <v>163119</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>25465</v>
+        <v>200197</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02458870967016811</v>
+        <v>0.2556902739256171</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0162584324010649</v>
+        <v>0.2297686792260264</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.03587048487263438</v>
+        <v>0.2819956789192741</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>56</v>
+        <v>542</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>39116</v>
+        <v>374078</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>29583</v>
+        <v>347688</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>50253</v>
+        <v>401842</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.02676524868582834</v>
+        <v>0.2559618583328436</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.02024218826644221</v>
+        <v>0.2379050566850428</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.03438564516267029</v>
+        <v>0.2749595756264286</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>275</v>
+        <v>765</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>192556</v>
+        <v>537314</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>173554</v>
+        <v>517554</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>211516</v>
+        <v>556219</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2562184092622987</v>
+        <v>0.7149602847356029</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2309344619126076</v>
+        <v>0.6886670219149457</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2814467573237918</v>
+        <v>0.7401154004517445</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>267</v>
+        <v>731</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>181522</v>
+        <v>510951</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>163119</v>
+        <v>490900</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>200197</v>
+        <v>528676</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2556902739256171</v>
+        <v>0.7197210164042148</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2297686792260264</v>
+        <v>0.6914777132122374</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2819956789192741</v>
+        <v>0.7446884119296957</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>542</v>
+        <v>1496</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>374078</v>
+        <v>1048265</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>347688</v>
+        <v>1016741</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>401842</v>
+        <v>1075236</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2559618583328436</v>
+        <v>0.717272892981328</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2379050566850428</v>
+        <v>0.6957027814548977</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2749595756264286</v>
+        <v>0.735728073611593</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>765</v>
+        <v>31</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>537314</v>
+        <v>21660</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>517554</v>
+        <v>15029</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>556219</v>
+        <v>30722</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7149602847356029</v>
+        <v>0.02882130600209834</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6886670219149457</v>
+        <v>0.01999755982558853</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7401154004517445</v>
+        <v>0.0408788372306081</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>731</v>
+        <v>25</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>510951</v>
+        <v>17456</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>490900</v>
+        <v>11542</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>528676</v>
+        <v>25465</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7197210164042148</v>
+        <v>0.02458870967016811</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6914777132122374</v>
+        <v>0.0162584324010649</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7446884119296957</v>
+        <v>0.03587048487263438</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1496</v>
+        <v>56</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1048265</v>
+        <v>39116</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1016741</v>
+        <v>29583</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1075236</v>
+        <v>50253</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.717272892981328</v>
+        <v>0.02676524868582834</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6957027814548977</v>
+        <v>0.02024218826644221</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.735728073611593</v>
+        <v>0.03438564516267029</v>
       </c>
     </row>
     <row r="19">
@@ -3484,205 +3484,205 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>669</v>
+        <v>24157</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>18133</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4089</v>
+        <v>30963</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.009865528040321972</v>
+        <v>0.3560419875966389</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>0.2672573085130184</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.0602665801232747</v>
+        <v>0.4563431936354252</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+        <v>16748</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>11974</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>22573</v>
+      </c>
       <c r="N4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
+        <v>0.2820555660654996</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>0.2016511182531943</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.3801514306526558</v>
+      </c>
       <c r="Q4" s="5" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>669</v>
+        <v>40905</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>0</v>
+        <v>32031</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>3317</v>
+        <v>49505</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.005261215636954463</v>
+        <v>0.3215119962019276</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0</v>
+        <v>0.2517596310214062</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.02607523105872736</v>
+        <v>0.3891039557340232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>24157</v>
+        <v>43023</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>18133</v>
+        <v>36184</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>30963</v>
+        <v>49250</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3560419875966389</v>
+        <v>0.6340924843630391</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2672573085130184</v>
+        <v>0.5333006144397743</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.4563431936354252</v>
+        <v>0.7258646415675438</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>16748</v>
+        <v>42630</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11974</v>
+        <v>36805</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>22573</v>
+        <v>47404</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2820555660654996</v>
+        <v>0.7179444339345004</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2016511182531943</v>
+        <v>0.6198485693473441</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.3801514306526558</v>
+        <v>0.7983488817468056</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>40905</v>
+        <v>85653</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>32031</v>
+        <v>76827</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>49505</v>
+        <v>94232</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.3215119962019276</v>
+        <v>0.673226788161118</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2517596310214062</v>
+        <v>0.6038498159502849</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.3891039557340232</v>
+        <v>0.7406550382257711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>43023</v>
+        <v>669</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>36184</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>49250</v>
+        <v>4089</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6340924843630391</v>
+        <v>0.009865528040321972</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5333006144397743</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7258646415675438</v>
+        <v>0.0602665801232747</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>42630</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>36805</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>47404</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="6" t="n">
-        <v>0.7179444339345004</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>0.6198485693473441</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0.7983488817468056</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="5" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>85653</v>
+        <v>669</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>76827</v>
+        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>94232</v>
+        <v>3317</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.673226788161118</v>
+        <v>0.005261215636954463</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.6038498159502849</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7406550382257711</v>
+        <v>0.02607523105872736</v>
       </c>
     </row>
     <row r="7">
@@ -3764,213 +3764,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>11</v>
+        <v>217</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7535</v>
+        <v>150127</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4071</v>
+        <v>133617</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>12858</v>
+        <v>166107</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01556646388883414</v>
+        <v>0.3101327925823008</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.00840894444405298</v>
+        <v>0.2760258381141196</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.0265614033509854</v>
+        <v>0.3431448438291904</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>15</v>
+        <v>198</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>9149</v>
+        <v>128326</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5089</v>
+        <v>112759</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>14708</v>
+        <v>143887</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01946760387198903</v>
+        <v>0.2730663418549517</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01082798945094826</v>
+        <v>0.2399403874128646</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.0312982038768992</v>
+        <v>0.3061797755576981</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>26</v>
+        <v>415</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>16684</v>
+        <v>278453</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>10923</v>
+        <v>255258</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>23694</v>
+        <v>300900</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01748814674192048</v>
+        <v>0.2918740366558057</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01144906670560069</v>
+        <v>0.2675612940069287</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.0248356284989991</v>
+        <v>0.3154028073077738</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>217</v>
+        <v>460</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>150127</v>
+        <v>326411</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>133617</v>
+        <v>310964</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>166107</v>
+        <v>343219</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3101327925823008</v>
+        <v>0.674300743528865</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2760258381141196</v>
+        <v>0.6423906679890063</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3431448438291904</v>
+        <v>0.7090235124498877</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>198</v>
+        <v>497</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>128326</v>
+        <v>332469</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>112759</v>
+        <v>315482</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>143887</v>
+        <v>348110</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2730663418549517</v>
+        <v>0.7074660542730593</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2399403874128646</v>
+        <v>0.6713186446351005</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3061797755576981</v>
+        <v>0.7407471331917624</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>415</v>
+        <v>957</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>278453</v>
+        <v>658880</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>255258</v>
+        <v>634904</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>300900</v>
+        <v>681137</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2918740366558057</v>
+        <v>0.6906378166022739</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2675612940069287</v>
+        <v>0.6655054395919895</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3154028073077738</v>
+        <v>0.7139677188768817</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>460</v>
+        <v>11</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>326411</v>
+        <v>7535</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>310964</v>
+        <v>4071</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>343219</v>
+        <v>12858</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.674300743528865</v>
+        <v>0.01556646388883414</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6423906679890063</v>
+        <v>0.00840894444405298</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7090235124498877</v>
+        <v>0.0265614033509854</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>497</v>
+        <v>15</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>332469</v>
+        <v>9149</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>315482</v>
+        <v>5089</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>348110</v>
+        <v>14708</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.7074660542730593</v>
+        <v>0.01946760387198903</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.6713186446351005</v>
+        <v>0.01082798945094826</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7407471331917624</v>
+        <v>0.0312982038768992</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>957</v>
+        <v>26</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>658880</v>
+        <v>16684</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>634904</v>
+        <v>10923</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>681137</v>
+        <v>23694</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.6906378166022739</v>
+        <v>0.01748814674192048</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6655054395919895</v>
+        <v>0.01144906670560069</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7139677188768817</v>
+        <v>0.0248356284989991</v>
       </c>
     </row>
     <row r="11">
@@ -4052,213 +4052,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3168</v>
+        <v>58309</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1281</v>
+        <v>48511</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7617</v>
+        <v>68552</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01700410077066587</v>
+        <v>0.312951457819857</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.006876392820484001</v>
+        <v>0.2603654046745338</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.04088288675195031</v>
+        <v>0.3679263692293663</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2997</v>
+        <v>61440</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1143</v>
+        <v>50833</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>6998</v>
+        <v>72028</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.01763528354467899</v>
+        <v>0.3615559225555067</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.006724814707958102</v>
+        <v>0.2991407411625779</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.04118396450082725</v>
+        <v>0.4238653683296996</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>6165</v>
+        <v>119748</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>3115</v>
+        <v>106101</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>10763</v>
+        <v>135210</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.01730517402913405</v>
+        <v>0.3361357162891161</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.008745025653810785</v>
+        <v>0.2978269423649675</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.03021295891801581</v>
+        <v>0.3795364383283888</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58309</v>
+        <v>124842</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>48511</v>
+        <v>114435</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>68552</v>
+        <v>135124</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.312951457819857</v>
+        <v>0.6700444414094772</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2603654046745338</v>
+        <v>0.6141867649524307</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3679263692293663</v>
+        <v>0.7252272150406033</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>61440</v>
+        <v>105495</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>50833</v>
+        <v>95457</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>72028</v>
+        <v>116060</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3615559225555067</v>
+        <v>0.6208087938998144</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2991407411625779</v>
+        <v>0.5617412331368222</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4238653683296996</v>
+        <v>0.6829815764840492</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>119748</v>
+        <v>230337</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>106101</v>
+        <v>214891</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>135210</v>
+        <v>244183</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3361357162891161</v>
+        <v>0.6465591096817498</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.2978269423649675</v>
+        <v>0.6032033793098157</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3795364383283888</v>
+        <v>0.6854271747549815</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>124842</v>
+        <v>3168</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>114435</v>
+        <v>1281</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>135124</v>
+        <v>7617</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6700444414094772</v>
+        <v>0.01700410077066587</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6141867649524307</v>
+        <v>0.006876392820484001</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7252272150406033</v>
+        <v>0.04088288675195031</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>105495</v>
+        <v>2997</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>95457</v>
+        <v>1143</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>116060</v>
+        <v>6998</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6208087938998144</v>
+        <v>0.01763528354467899</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5617412331368222</v>
+        <v>0.006724814707958102</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6829815764840492</v>
+        <v>0.04118396450082725</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>335</v>
+        <v>10</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>230337</v>
+        <v>6165</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>214891</v>
+        <v>3115</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>244183</v>
+        <v>10763</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6465591096817498</v>
+        <v>0.01730517402913405</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6032033793098157</v>
+        <v>0.008745025653810785</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6854271747549815</v>
+        <v>0.03021295891801581</v>
       </c>
     </row>
     <row r="15">
@@ -4340,213 +4340,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>11373</v>
+        <v>232593</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>6534</v>
+        <v>211213</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17383</v>
+        <v>253967</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01540533868527224</v>
+        <v>0.3150635773624768</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.008850896009006877</v>
+        <v>0.2861024106694964</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02354584038101045</v>
+        <v>0.3440162031320989</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>12145</v>
+        <v>206513</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>7840</v>
+        <v>185452</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>18275</v>
+        <v>225030</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01736918897859021</v>
+        <v>0.2953341816490889</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0112119473229022</v>
+        <v>0.2652139349537481</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02613524002767794</v>
+        <v>0.3218151736648645</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>38</v>
+        <v>651</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>23518</v>
+        <v>439106</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>17054</v>
+        <v>413010</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>32294</v>
+        <v>468639</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01636063138259591</v>
+        <v>0.3054664366273929</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.01186368418093788</v>
+        <v>0.2873125050273043</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.02246525665392955</v>
+        <v>0.326011047099263</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>335</v>
+        <v>702</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>232593</v>
+        <v>494276</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>211213</v>
+        <v>473777</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>253967</v>
+        <v>515717</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3150635773624768</v>
+        <v>0.6695310839522509</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2861024106694964</v>
+        <v>0.6417632730683875</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3440162031320989</v>
+        <v>0.6985747199617873</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>316</v>
+        <v>716</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>206513</v>
+        <v>480594</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>185452</v>
+        <v>461458</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>225030</v>
+        <v>500683</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2953341816490889</v>
+        <v>0.6872966293723209</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2652139349537481</v>
+        <v>0.6599298932045679</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3218151736648645</v>
+        <v>0.7160248723910149</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>651</v>
+        <v>1418</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>439106</v>
+        <v>974870</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>413010</v>
+        <v>945109</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>468639</v>
+        <v>1001563</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.3054664366273929</v>
+        <v>0.6781729319900112</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2873125050273043</v>
+        <v>0.6574696323566337</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.326011047099263</v>
+        <v>0.6967418884415597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>702</v>
+        <v>18</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>494276</v>
+        <v>11373</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>473777</v>
+        <v>6534</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>515717</v>
+        <v>17383</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.6695310839522509</v>
+        <v>0.01540533868527224</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6417632730683875</v>
+        <v>0.008850896009006877</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.6985747199617873</v>
+        <v>0.02354584038101045</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>716</v>
+        <v>20</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>480594</v>
+        <v>12145</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>461458</v>
+        <v>7840</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>500683</v>
+        <v>18275</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.6872966293723209</v>
+        <v>0.01736918897859021</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6599298932045679</v>
+        <v>0.0112119473229022</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7160248723910149</v>
+        <v>0.02613524002767794</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1418</v>
+        <v>38</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>974870</v>
+        <v>23518</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>945109</v>
+        <v>17054</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1001563</v>
+        <v>32294</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.6781729319900112</v>
+        <v>0.01636063138259591</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6574696323566337</v>
+        <v>0.01186368418093788</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.6967418884415597</v>
+        <v>0.02246525665392955</v>
       </c>
     </row>
     <row r="19">
@@ -4859,205 +4859,205 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>424</v>
+        <v>19991</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>14132</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2327</v>
+        <v>26573</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.0074706397552454</v>
+        <v>0.3523787235397481</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>0.2491025043954186</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.04101349476539392</v>
+        <v>0.4683952233578466</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+        <v>16134</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>11009</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>22052</v>
+      </c>
       <c r="N4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
+        <v>0.3534757291830145</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>0.2411983449415787</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.4831162255419912</v>
+      </c>
       <c r="Q4" s="5" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>424</v>
+        <v>36126</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>0</v>
+        <v>27939</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>2190</v>
+        <v>44443</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.004139836533328114</v>
+        <v>0.3528678262204774</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0</v>
+        <v>0.2729002030817265</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.02139236786798283</v>
+        <v>0.4341087585391257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>19991</v>
+        <v>36317</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>14132</v>
+        <v>29612</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>26573</v>
+        <v>42217</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.3523787235397481</v>
+        <v>0.6401506367050065</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.2491025043954186</v>
+        <v>0.5219621942167683</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.4683952233578466</v>
+        <v>0.7441531937552809</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>16134</v>
+        <v>29511</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>11009</v>
+        <v>23593</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>22052</v>
+        <v>34636</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3534757291830145</v>
+        <v>0.6465242708169855</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.2411983449415787</v>
+        <v>0.5168837744580088</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.4831162255419912</v>
+        <v>0.7588016550584213</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>36126</v>
+        <v>65828</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>27939</v>
+        <v>57663</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>44443</v>
+        <v>74079</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.3528678262204774</v>
+        <v>0.6429923372461945</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.2729002030817265</v>
+        <v>0.5632372184032218</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.4341087585391257</v>
+        <v>0.7235820560393572</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>36317</v>
+        <v>424</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>29612</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>42217</v>
+        <v>2327</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6401506367050065</v>
+        <v>0.0074706397552454</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5219621942167683</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.7441531937552809</v>
+        <v>0.04101349476539392</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>29511</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>23593</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>34636</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="6" t="n">
-        <v>0.6465242708169855</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>0.5168837744580088</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0.7588016550584213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="5" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>65828</v>
+        <v>424</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>57663</v>
+        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>74079</v>
+        <v>2190</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.6429923372461945</v>
+        <v>0.004139836533328114</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.5632372184032218</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.7235820560393572</v>
+        <v>0.02139236786798283</v>
       </c>
     </row>
     <row r="7">
@@ -5139,213 +5139,213 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5226</v>
+        <v>137570</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1649</v>
+        <v>117606</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>13010</v>
+        <v>155095</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01103119953987279</v>
+        <v>0.2903704208334738</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.003479652556551123</v>
+        <v>0.2482319345485959</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.02745988284053201</v>
+        <v>0.3273611502880264</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>10</v>
+        <v>203</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>7915</v>
+        <v>117565</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3850</v>
+        <v>104569</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>14242</v>
+        <v>132086</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.01843961277230586</v>
+        <v>0.2739002976642553</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.008970323130752848</v>
+        <v>0.2436219946645183</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.0331808671578324</v>
+        <v>0.3077289765952519</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>15</v>
+        <v>424</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>13141</v>
+        <v>255136</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>7320</v>
+        <v>231917</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>22186</v>
+        <v>279466</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.01455267103263844</v>
+        <v>0.2825416095343376</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.008105937981847219</v>
+        <v>0.2568291869587502</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.02456870436503458</v>
+        <v>0.3094855765689143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>221</v>
+        <v>428</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>137570</v>
+        <v>330978</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>117606</v>
+        <v>312822</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>155095</v>
+        <v>350235</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2903704208334738</v>
+        <v>0.6985983796266534</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.2482319345485959</v>
+        <v>0.6602758389592023</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.3273611502880264</v>
+        <v>0.7392454069095776</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>203</v>
+        <v>426</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>117565</v>
+        <v>303747</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>104569</v>
+        <v>288142</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>132086</v>
+        <v>317224</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2739002976642553</v>
+        <v>0.707660089563439</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.2436219946645183</v>
+        <v>0.671304260731142</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0.3077289765952519</v>
+        <v>0.7390586653236124</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>424</v>
+        <v>854</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>255136</v>
+        <v>634725</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>231917</v>
+        <v>609311</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>279466</v>
+        <v>658677</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0.2825416095343376</v>
+        <v>0.7029057194330239</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.2568291869587502</v>
+        <v>0.6747611324310935</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0.3094855765689143</v>
+        <v>0.7294302616366944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>428</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>330978</v>
+        <v>5226</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>312822</v>
+        <v>1649</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>350235</v>
+        <v>13010</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.6985983796266534</v>
+        <v>0.01103119953987279</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6602758389592023</v>
+        <v>0.003479652556551123</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.7392454069095776</v>
+        <v>0.02745988284053201</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>426</v>
+        <v>10</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>303747</v>
+        <v>7915</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>288142</v>
+        <v>3850</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>317224</v>
+        <v>14242</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.707660089563439</v>
+        <v>0.01843961277230586</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.671304260731142</v>
+        <v>0.008970323130752848</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.7390586653236124</v>
+        <v>0.0331808671578324</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>854</v>
+        <v>15</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>634725</v>
+        <v>13141</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>609311</v>
+        <v>7320</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>658677</v>
+        <v>22186</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.7029057194330239</v>
+        <v>0.01455267103263844</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.6747611324310935</v>
+        <v>0.008105937981847219</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.7294302616366944</v>
+        <v>0.02456870436503458</v>
       </c>
     </row>
     <row r="11">
@@ -5427,213 +5427,213 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1842</v>
+        <v>37840</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>29204</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>6434</v>
+        <v>46884</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.01093586726598701</v>
+        <v>0.2246803795471455</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>0.1734037572858866</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03820083778262561</v>
+        <v>0.2783778574495384</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1248</v>
+        <v>37299</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>28846</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>5117</v>
+        <v>45834</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.008433528322805448</v>
+        <v>0.25198124988928</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>0.1948737263672465</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.03457029780790831</v>
+        <v>0.3096441516919644</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>3090</v>
+        <v>75139</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>879</v>
+        <v>62875</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>8384</v>
+        <v>87303</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.009765340646079656</v>
+        <v>0.2374509898472341</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.002778105471197746</v>
+        <v>0.1986946645467076</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.02649314925541104</v>
+        <v>0.275889652879252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>37840</v>
+        <v>128737</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>29204</v>
+        <v>119510</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>46884</v>
+        <v>137462</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2246803795471455</v>
+        <v>0.7643837531868675</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1734037572858866</v>
+        <v>0.7095985423579519</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2783778574495384</v>
+        <v>0.8161887114053741</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>64</v>
+        <v>162</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>37299</v>
+        <v>109476</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>28846</v>
+        <v>101033</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>45834</v>
+        <v>118239</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.25198124988928</v>
+        <v>0.7395852217879146</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1948737263672465</v>
+        <v>0.6825493161314826</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3096441516919644</v>
+        <v>0.7987854226327543</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>129</v>
+        <v>333</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>75139</v>
+        <v>238212</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>62875</v>
+        <v>225601</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>87303</v>
+        <v>250661</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2374509898472341</v>
+        <v>0.7527836695066861</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1986946645467076</v>
+        <v>0.7129320754033664</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.275889652879252</v>
+        <v>0.7921261707861811</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>171</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>128737</v>
+        <v>1842</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>119510</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>137462</v>
+        <v>6434</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7643837531868675</v>
+        <v>0.01093586726598701</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7095985423579519</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8161887114053741</v>
+        <v>0.03820083778262561</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>109476</v>
+        <v>1248</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>101033</v>
+        <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>118239</v>
+        <v>5117</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7395852217879146</v>
+        <v>0.008433528322805448</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6825493161314826</v>
+        <v>0</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7987854226327543</v>
+        <v>0.03457029780790831</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>333</v>
+        <v>4</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>238212</v>
+        <v>3090</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>225601</v>
+        <v>879</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>250661</v>
+        <v>8384</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7527836695066861</v>
+        <v>0.009765340646079656</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7129320754033664</v>
+        <v>0.002778105471197746</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7921261707861811</v>
+        <v>0.02649314925541104</v>
       </c>
     </row>
     <row r="15">
@@ -5715,213 +5715,213 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Más</t>
+          <t>Menos</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>7492</v>
+        <v>195402</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3359</v>
+        <v>173560</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16163</v>
+        <v>217575</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.01071921357550712</v>
+        <v>0.2795744929608477</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.004805967813107631</v>
+        <v>0.2483245280293698</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02312589527033307</v>
+        <v>0.3112999254701128</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>9163</v>
+        <v>170999</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4640</v>
+        <v>153821</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>15763</v>
+        <v>189776</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01471055891067521</v>
+        <v>0.2745227696843488</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.007449848397985451</v>
+        <v>0.2469442564305586</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.02530581619824738</v>
+        <v>0.3046667173353083</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>20</v>
+        <v>606</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>16655</v>
+        <v>366401</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>10467</v>
+        <v>339697</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>27125</v>
+        <v>395115</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.01260009747036753</v>
+        <v>0.2771939159487967</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.007918972473508357</v>
+        <v>0.2569917190872997</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.0205208739405985</v>
+        <v>0.2989171151477567</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Menos</t>
+          <t>Igual</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>315</v>
+        <v>652</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>195402</v>
+        <v>496031</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>173560</v>
+        <v>473783</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>217575</v>
+        <v>518880</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.2795744929608477</v>
+        <v>0.7097062934636452</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.2483245280293698</v>
+        <v>0.6778740019407858</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3112999254701128</v>
+        <v>0.7423967959422112</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>291</v>
+        <v>630</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>170999</v>
+        <v>442734</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>153821</v>
+        <v>423999</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>189776</v>
+        <v>460413</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.2745227696843488</v>
+        <v>0.7107666714049761</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.2469442564305586</v>
+        <v>0.6806906195226125</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.3046667173353083</v>
+        <v>0.7391487131648633</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>606</v>
+        <v>1282</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>366401</v>
+        <v>938765</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>339697</v>
+        <v>909859</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>395115</v>
+        <v>966511</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.2771939159487967</v>
+        <v>0.7102059865808358</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.2569917190872997</v>
+        <v>0.6883373299523707</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2989171151477567</v>
+        <v>0.7311966736859681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Más</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>652</v>
+        <v>8</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>496031</v>
+        <v>7492</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>473783</v>
+        <v>3359</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>518880</v>
+        <v>16163</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7097062934636452</v>
+        <v>0.01071921357550712</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6778740019407858</v>
+        <v>0.004805967813107631</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.7423967959422112</v>
+        <v>0.02312589527033307</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>630</v>
+        <v>12</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>442734</v>
+        <v>9163</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>423999</v>
+        <v>4640</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>460413</v>
+        <v>15763</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.7107666714049761</v>
+        <v>0.01471055891067521</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.6806906195226125</v>
+        <v>0.007449848397985451</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.7391487131648633</v>
+        <v>0.02530581619824738</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1282</v>
+        <v>20</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>938765</v>
+        <v>16655</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>909859</v>
+        <v>10467</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>966511</v>
+        <v>27125</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.7102059865808358</v>
+        <v>0.01260009747036753</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.6883373299523707</v>
+        <v>0.007918972473508357</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.7311966736859681</v>
+        <v>0.0205208739405985</v>
       </c>
     </row>
     <row r="19">
